--- a/src_excel/Macronutriments.xlsx
+++ b/src_excel/Macronutriments.xlsx
@@ -1,46 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fayol\OneDrive\Documents\Essai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manah\Documents\nutrition\src_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D714667A-D827-4B0A-AC56-16CC3589BF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6AC4441D-BD32-4101-93BF-4145874921E7}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
-  <si>
-    <t xml:space="preserve">UNITE </t>
-  </si>
-  <si>
-    <t>g/100g</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Lipides</t>
   </si>
@@ -51,9 +35,6 @@
     <t>Glucides</t>
   </si>
   <si>
-    <t>Kcal/100g</t>
-  </si>
-  <si>
     <t>Proteines</t>
   </si>
   <si>
@@ -69,25 +50,34 @@
     <t>Essai2_K067_Lentille_verte</t>
   </si>
   <si>
+    <t>Essai3_K067_Lentille_verte</t>
+  </si>
+  <si>
+    <t>Essai1_K068_Lentille_corail</t>
+  </si>
+  <si>
+    <t>Essai2_K068_Lentille_corail</t>
+  </si>
+  <si>
+    <t>Essai3_K068_Lentille_corail</t>
+  </si>
+  <si>
+    <t>Essai1_K069_Lentille_noire</t>
+  </si>
+  <si>
+    <t>Essai2_K069_Lentille_noire</t>
+  </si>
+  <si>
+    <t>Essai3_K069_Lentille_noire</t>
+  </si>
+  <si>
     <t>Moyenne_K067_Lentille_verte</t>
   </si>
   <si>
-    <t>Essai2_K068_Lentille_corail</t>
-  </si>
-  <si>
     <t>Moyenne_K068_Lentille_corail</t>
   </si>
   <si>
-    <t>Essai1_K069_Lentille_noire</t>
-  </si>
-  <si>
-    <t>Essai2_K069_Lentille_noire</t>
-  </si>
-  <si>
     <t>Moyenne_K069_Lentille_noire</t>
-  </si>
-  <si>
-    <t>Essai1_K068_Lentille_corail</t>
   </si>
   <si>
     <t>PARAMETRES</t>
@@ -96,7 +86,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -127,7 +117,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -159,11 +149,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -174,8 +182,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -195,7 +209,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -490,271 +504,313 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A49071-C4EB-4BBF-AAB5-64DDF3915541}">
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="I1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="2" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="B2" s="2">
+        <v>25.67</v>
       </c>
       <c r="C2" s="2">
-        <v>25.68</v>
+        <v>25.66</v>
       </c>
       <c r="D2" s="2">
         <v>25.62</v>
       </c>
-      <c r="E2" s="4">
-        <f t="shared" ref="E2:E7" si="0">AVERAGE(C2,D2)</f>
-        <v>25.65</v>
+      <c r="E2" s="3">
+        <f>AVERAGE(B2:D2)</f>
+        <v>25.650000000000002</v>
       </c>
       <c r="F2" s="2">
+        <v>25.81</v>
+      </c>
+      <c r="G2" s="2">
         <v>25.8</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2">
         <v>25.82</v>
       </c>
-      <c r="H2" s="4">
-        <f t="shared" ref="H2:H7" si="1">AVERAGE(F2,G2)</f>
+      <c r="I2" s="3">
+        <f>AVERAGE(F2:H2)</f>
         <v>25.810000000000002</v>
       </c>
-      <c r="I2" s="2">
+      <c r="J2" s="2">
         <v>23.26</v>
       </c>
-      <c r="J2" s="2">
+      <c r="K2" s="4">
         <v>23.32</v>
       </c>
-      <c r="K2" s="4">
-        <f t="shared" ref="K2:K7" si="2">AVERAGE(I2,J2)</f>
+      <c r="L2" s="4">
         <v>23.29</v>
       </c>
+      <c r="M2" s="6">
+        <f>AVERAGE(J2:L2)</f>
+        <v>23.290000000000003</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.77</v>
       </c>
       <c r="C3" s="2">
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
       <c r="D3" s="2">
         <v>0.97</v>
       </c>
-      <c r="E3" s="4">
-        <f t="shared" si="0"/>
-        <v>0.87</v>
+      <c r="E3" s="3">
+        <f t="shared" ref="E3:E7" si="0">AVERAGE(B3:D3)</f>
+        <v>0.87000000000000011</v>
       </c>
       <c r="F3" s="2">
+        <v>1.28</v>
+      </c>
+      <c r="G3" s="2">
         <v>1.31</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
         <v>1.26</v>
       </c>
-      <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2850000000000001</v>
-      </c>
-      <c r="I3" s="2">
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I7" si="1">AVERAGE(F3:H3)</f>
+        <v>1.2833333333333332</v>
+      </c>
+      <c r="J3" s="2">
         <v>0.98</v>
       </c>
-      <c r="J3" s="2">
+      <c r="K3" s="4">
         <v>0.97</v>
       </c>
-      <c r="K3" s="4">
-        <f t="shared" si="2"/>
-        <v>0.97499999999999998</v>
+      <c r="L3" s="4">
+        <v>0.97</v>
+      </c>
+      <c r="M3" s="6">
+        <f t="shared" ref="M3:M7" si="2">AVERAGE(J3:L3)</f>
+        <v>0.97333333333333327</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="B4" s="2">
+        <v>3.78</v>
+      </c>
       <c r="C4" s="2">
-        <v>3.78</v>
+        <v>3.65</v>
       </c>
       <c r="D4" s="2">
         <v>3.53</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <f t="shared" si="0"/>
-        <v>3.6549999999999998</v>
+        <v>3.6533333333333329</v>
       </c>
       <c r="F4" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G4" s="2">
         <v>2.4500000000000002</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>2.16</v>
       </c>
-      <c r="H4" s="4">
+      <c r="I4" s="3">
         <f t="shared" si="1"/>
-        <v>2.3050000000000002</v>
-      </c>
-      <c r="I4" s="2">
+        <v>2.3033333333333332</v>
+      </c>
+      <c r="J4" s="2">
         <v>3.11</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="4">
         <v>3.22</v>
       </c>
-      <c r="K4" s="4">
+      <c r="L4" s="4">
+        <v>3.16</v>
+      </c>
+      <c r="M4" s="6">
         <f t="shared" si="2"/>
-        <v>3.165</v>
+        <v>3.1633333333333336</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>9.42</v>
       </c>
       <c r="C5" s="2">
-        <v>9.42</v>
+        <v>9.52</v>
       </c>
       <c r="D5" s="2">
         <v>9.6300000000000008</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <f t="shared" si="0"/>
-        <v>9.5250000000000004</v>
+        <v>9.5233333333333334</v>
       </c>
       <c r="F5" s="2">
+        <v>11.96</v>
+      </c>
+      <c r="G5" s="2">
         <v>11.87</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <v>12.05</v>
       </c>
-      <c r="H5" s="4">
+      <c r="I5" s="3">
         <f t="shared" si="1"/>
-        <v>11.96</v>
-      </c>
-      <c r="I5" s="2">
+        <v>11.959999999999999</v>
+      </c>
+      <c r="J5" s="2">
         <v>10.39</v>
       </c>
-      <c r="J5" s="2">
+      <c r="K5" s="4">
         <v>10.41</v>
       </c>
-      <c r="K5" s="4">
+      <c r="L5" s="4">
+        <v>10.4</v>
+      </c>
+      <c r="M5" s="6">
         <f t="shared" si="2"/>
         <v>10.4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B6" s="2">
+        <v>60.35</v>
       </c>
       <c r="C6" s="2">
-        <v>60.35</v>
+        <v>60.31</v>
       </c>
       <c r="D6" s="2">
         <v>60.25</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <f t="shared" si="0"/>
-        <v>60.3</v>
+        <v>60.303333333333335</v>
       </c>
       <c r="F6" s="2">
+        <v>58.64</v>
+      </c>
+      <c r="G6" s="2">
         <v>58.57</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <v>58.71</v>
       </c>
-      <c r="H6" s="4">
+      <c r="I6" s="3">
         <f t="shared" si="1"/>
-        <v>58.64</v>
-      </c>
-      <c r="I6" s="2">
+        <v>58.640000000000008</v>
+      </c>
+      <c r="J6" s="2">
         <v>62.26</v>
       </c>
-      <c r="J6" s="2">
+      <c r="K6" s="4">
         <v>63.08</v>
       </c>
-      <c r="K6" s="4">
+      <c r="L6" s="4">
+        <v>62.67</v>
+      </c>
+      <c r="M6" s="6">
         <f t="shared" si="2"/>
-        <v>62.67</v>
+        <v>62.669999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="B7" s="2">
+        <v>351.05</v>
+      </c>
       <c r="C7" s="2">
-        <v>351.05</v>
+        <v>351.62</v>
       </c>
       <c r="D7" s="2">
         <v>352.21</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <f t="shared" si="0"/>
-        <v>351.63</v>
+        <v>351.62666666666672</v>
       </c>
       <c r="F7" s="2">
+        <v>349.36</v>
+      </c>
+      <c r="G7" s="2">
         <v>349.27</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>349.46</v>
       </c>
-      <c r="H7" s="4">
+      <c r="I7" s="3">
         <f t="shared" si="1"/>
-        <v>349.36500000000001</v>
-      </c>
-      <c r="I7" s="2">
+        <v>349.36333333333329</v>
+      </c>
+      <c r="J7" s="2">
         <v>350.9</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="4">
         <v>354.21</v>
       </c>
-      <c r="K7" s="4">
+      <c r="L7" s="4">
+        <v>352.55</v>
+      </c>
+      <c r="M7" s="6">
         <f t="shared" si="2"/>
-        <v>352.55499999999995</v>
+        <v>352.55333333333328</v>
       </c>
     </row>
   </sheetData>
